--- a/請購單 採購單資料.xlsx
+++ b/請購單 採購單資料.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\Purchase system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8977144-45A0-4000-B60E-FF20881FCE8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9872716B-0048-4BBC-B8B8-709834B9D447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purchase Orders'!$A$1:$N$250</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
